--- a/artfynd/A 28836-2022 artfynd.xlsx
+++ b/artfynd/A 28836-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28836-2022 artfynd.xlsx
+++ b/artfynd/A 28836-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1039,112 +1039,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>119137063</v>
-      </c>
-      <c r="B5" t="n">
-        <v>101269</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>221333</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Backklöver</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Trifolium montanum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Dyvik, Upl</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>721707</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6640148</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Norrtälje</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Vätö</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2024-06-18</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2024-06-18</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Karin Agstam-Norlin</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Karin Agstam-Norlin</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28836-2022 artfynd.xlsx
+++ b/artfynd/A 28836-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>94499215</v>
       </c>
       <c r="B2" t="n">
-        <v>56859</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -722,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>722412.1116719937</v>
+        <v>722412</v>
       </c>
       <c r="R2" t="n">
-        <v>6640739.120328019</v>
+        <v>6640739</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,19 +750,9 @@
           <t>2021-06-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-06-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,12 +782,7 @@
         <v>95907760</v>
       </c>
       <c r="B3" t="n">
-        <v>55649</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -847,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>722412.1116719937</v>
+        <v>722412</v>
       </c>
       <c r="R3" t="n">
-        <v>6640739.120328019</v>
+        <v>6640739</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,19 +860,9 @@
           <t>2021-09-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,53 +890,52 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>72871343</v>
+        <v>119137062</v>
       </c>
       <c r="B4" t="n">
-        <v>99590</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221333</v>
+        <v>219875</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Backklöver</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Trifolium montanum</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dyvik, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721706.6784319634</v>
+        <v>721683</v>
       </c>
       <c r="R4" t="n">
-        <v>6640148.217632387</v>
+        <v>6640155</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,22 +959,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-06-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-06-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,23 +976,124 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Karin Agstam-Norlin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Karin Agstam-Norlin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>72871343</v>
+      </c>
+      <c r="B5" t="n">
+        <v>102443</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221333</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Backklöver</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Trifolium montanum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Dyvik, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>721707</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6640148</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vätö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2018-06-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2018-06-13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Johan Lilja</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Johan Lilja</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 28836-2022 artfynd.xlsx
+++ b/artfynd/A 28836-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94499215</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95907760</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119137062</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,8 +1118,19 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72871343</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>